--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90902</v>
+        <v>90905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90905</v>
+        <v>90908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90908</v>
+        <v>90912</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90912</v>
+        <v>90919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90919</v>
+        <v>90921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90927</v>
+        <v>90931</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90931</v>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90932</v>
+        <v>90935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41993-2021 artfynd.xlsx
+++ b/artfynd/A 41993-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129150425</v>
       </c>
       <c r="B2" t="n">
-        <v>90935</v>
+        <v>90963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
